--- a/rabbit-web-app/public/sample_excels/dispatch/customer_single_sample.xlsx
+++ b/rabbit-web-app/public/sample_excels/dispatch/customer_single_sample.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Customer" sheetId="1" r:id="rId1"/>
+    <sheet name="Customers" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -398,13 +398,6 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:E2"/>
-  <cols>
-    <col min="1" max="1" width="28.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="55.83203125" customWidth="1"/>
-    <col min="5" max="5" width="12.83203125" customWidth="1"/>
-  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -420,7 +413,7 @@
         <v>address</v>
       </c>
       <c r="E1" t="str">
-        <v>pinCode</v>
+        <v>zipCode</v>
       </c>
     </row>
     <row r="2">
@@ -431,7 +424,7 @@
         <v>supplychain@tataconsumer.com</v>
       </c>
       <c r="C2" t="str">
-        <v>+91 22 6665 8282</v>
+        <v>22 6665 8282</v>
       </c>
       <c r="D2" t="str">
         <v>11/13 Botawala Building, Horniman Circle, Fort, Mumbai, Maharashtra</v>
